--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488091_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488091_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.308400000000001</v>
+        <v>7.9455</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3878</v>
+        <v>4.7829</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9207</v>
+        <v>3.1625</v>
       </c>
       <c r="G2" t="n">
         <v>5.5221</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5376</v>
+        <v>1.1746</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1749</v>
+        <v>0.57</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3627</v>
+        <v>0.6046</v>
       </c>
       <c r="V2" t="n">
         <v>-0.337</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7076</v>
+        <v>4.9563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8722</v>
+        <v>1.812</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8354</v>
+        <v>3.1443</v>
       </c>
       <c r="G3" t="n">
         <v>3.459</v>
@@ -688,13 +688,13 @@
         <v>3.1716</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4936</v>
+        <v>-0.245</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0497</v>
+        <v>-0.11</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4439</v>
+        <v>-0.135</v>
       </c>
       <c r="V3" t="n">
         <v>1.5441</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3304</v>
+        <v>4.0198</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5114</v>
+        <v>1.0042</v>
       </c>
       <c r="F4" t="n">
-        <v>2.819</v>
+        <v>3.0156</v>
       </c>
       <c r="G4" t="n">
         <v>3.2227</v>
@@ -766,13 +766,13 @@
         <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5553</v>
+        <v>0.134</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4844</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.1256</v>
       </c>
       <c r="V4" t="n">
         <v>0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1173</v>
+        <v>3.1747</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1076</v>
+        <v>0.7532</v>
       </c>
       <c r="F5" t="n">
-        <v>2.225</v>
+        <v>2.4215</v>
       </c>
       <c r="G5" t="n">
         <v>1.5729</v>
@@ -844,13 +844,13 @@
         <v>2.5769</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3079</v>
+        <v>-0.2505</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.0641</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.383</v>
+        <v>-0.1864</v>
       </c>
       <c r="V5" t="n">
         <v>0.2666</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.322</v>
+        <v>1.1277</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4385</v>
+        <v>0.9916</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1165</v>
+        <v>0.1362</v>
       </c>
       <c r="G6" t="n">
         <v>0.3071</v>
@@ -922,13 +922,13 @@
         <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5063</v>
+        <v>0.3121</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6829</v>
+        <v>0.236</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1766</v>
+        <v>0.0761</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4737</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0188</v>
+        <v>1.0957</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6898</v>
+        <v>-2.276</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7086</v>
+        <v>3.3717</v>
       </c>
       <c r="G7" t="n">
         <v>0.2303</v>
@@ -1000,13 +1000,13 @@
         <v>2.7751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2908</v>
+        <v>-0.2139</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.433</v>
+        <v>-0.0191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1422</v>
+        <v>-0.1948</v>
       </c>
       <c r="V7" t="n">
         <v>1.2775</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1088</v>
+        <v>-0.2925</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6421</v>
+        <v>-1.9872</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7509</v>
+        <v>1.6947</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8193</v>
@@ -1156,13 +1156,13 @@
         <v>2.7751</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2452</v>
+        <v>-0.156</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4333</v>
+        <v>0.0883</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1881</v>
+        <v>-0.2442</v>
       </c>
       <c r="V9" t="n">
         <v>1.8811</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8638</v>
+        <v>-0.6028</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.616</v>
+        <v>-0.327</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2478</v>
+        <v>-0.2758</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1086</v>
@@ -1234,13 +1234,13 @@
         <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2904</v>
+        <v>-0.0294</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.312</v>
+        <v>-0.0229</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0216</v>
+        <v>-0.0065</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2666</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3697</v>
+        <v>-1.0297</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5094</v>
+        <v>-2.1414</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1398</v>
+        <v>1.1117</v>
       </c>
       <c r="G11" t="n">
         <v>0.2806</v>
@@ -1312,13 +1312,13 @@
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1766</v>
+        <v>0.1633</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.301</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1243</v>
+        <v>0.0963</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4737</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1985</v>
+        <v>-2.8762</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.6254</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3069</v>
+        <v>-2.2507</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8454</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4214</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1872</v>
+        <v>0.0789</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7098</v>
+        <v>-3.5279</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8284</v>
+        <v>-2.5622</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8814</v>
+        <v>-0.9656</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5245</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.203</v>
+        <v>-0.0211</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1872</v>
+        <v>0.0789</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0158</v>
+        <v>-0.1001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.963</v>
+        <v>-5.31</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6731</v>
+        <v>-1.3009</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.2899</v>
+        <v>-4.0091</v>
       </c>
       <c r="G14" t="n">
         <v>-1.828</v>
@@ -1546,13 +1546,13 @@
         <v>2.7751</v>
       </c>
       <c r="S14" t="n">
-        <v>0.202</v>
+        <v>-0.145</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8005</v>
+        <v>0.1727</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5985</v>
+        <v>-0.3177</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1476</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.713799999999998</v>
+        <v>9.585899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.8428</v>
+        <v>-0.9708999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10.5569</v>
+        <v>10.557</v>
       </c>
       <c r="G15" t="n">
         <v>9.374200000000002</v>
@@ -1624,13 +1624,13 @@
         <v>21.8045</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2479</v>
+        <v>0.6240000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7878000000000001</v>
+        <v>1.0842</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4603</v>
+        <v>-0.4602</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4032</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0243</v>
+        <v>2.48</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1304</v>
+        <v>1.7278</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8939</v>
+        <v>0.7522</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2171</v>
+        <v>1.7188</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3426</v>
+        <v>0.1614</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8746</v>
+        <v>1.5573</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2887</v>
+        <v>1.6489</v>
       </c>
       <c r="K16" t="n">
-        <v>0.128</v>
+        <v>0.3632</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1607</v>
+        <v>1.2857</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5058</v>
+        <v>0.0699</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4705</v>
+        <v>-0.2018</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0353</v>
+        <v>0.2717</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3787</v>
+        <v>0.9911</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3787</v>
+        <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2592</v>
+        <v>0.0367</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3085</v>
+        <v>0.0789</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9507</v>
+        <v>-0.0422</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6036</v>
+        <v>-0.2666</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0704</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2201</v>
+        <v>2.3239</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5241</v>
+        <v>3.7953</v>
       </c>
       <c r="F17" t="n">
-        <v>0.696</v>
+        <v>-1.4715</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7188</v>
+        <v>1.467</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1614</v>
+        <v>-0.624</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5573</v>
+        <v>2.091</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6489</v>
+        <v>3.7165</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3632</v>
+        <v>0.5788</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2857</v>
+        <v>3.1377</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0699</v>
+        <v>-2.2495</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2018</v>
+        <v>-1.2028</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2717</v>
+        <v>-1.0467</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>2.3787</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2232</v>
+        <v>-0.1432</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1248</v>
+        <v>-0.3532</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0984</v>
+        <v>0.21</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7068</v>
+        <v>1.9736</v>
       </c>
       <c r="E18" t="n">
-        <v>3.286</v>
+        <v>0.9266</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5792</v>
+        <v>1.047</v>
       </c>
       <c r="G18" t="n">
-        <v>1.467</v>
+        <v>-2.2171</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.624</v>
+        <v>-1.3426</v>
       </c>
       <c r="I18" t="n">
-        <v>2.091</v>
+        <v>-0.8746</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7165</v>
+        <v>0.2887</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5788</v>
+        <v>0.128</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1377</v>
+        <v>0.1607</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2495</v>
+        <v>-2.5058</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2028</v>
+        <v>-1.4705</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0467</v>
+        <v>-1.0353</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3964</v>
+        <v>2.3787</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>2.3787</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7602</v>
+        <v>1.2086</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8625</v>
+        <v>0.1048</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1023</v>
+        <v>1.1038</v>
       </c>
       <c r="V18" t="n">
         <v>0.6036</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4142</v>
+        <v>0.5331</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8107</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5302</v>
+        <v>1.8815</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5625</v>
+        <v>0.9699</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9677</v>
+        <v>0.9116</v>
       </c>
       <c r="G19" t="n">
         <v>0.026</v>
@@ -1936,13 +1936,13 @@
         <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2798</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2496</v>
+        <v>0.1579</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0302</v>
+        <v>-0.0864</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>S. TORRECILLAS  LAJARA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4179</v>
+        <v>0.9053</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5442</v>
+        <v>0.9053</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1263</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3145</v>
+        <v>0.9053</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7451</v>
+        <v>0.3027</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4306</v>
+        <v>0.6027</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4229</v>
+        <v>0.9053</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3386</v>
+        <v>0.3027</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0842</v>
+        <v>0.6027</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1084</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5936</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5148</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7158</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1036</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3878</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS  LAJARA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9053</v>
+        <v>0.3417</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9053</v>
+        <v>0.2199</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.1218</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9053</v>
+        <v>0.3145</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3027</v>
+        <v>0.7451</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6027</v>
+        <v>-0.4306</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9053</v>
+        <v>1.4229</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3027</v>
+        <v>1.3386</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6027</v>
+        <v>0.0842</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-1.1084</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.5936</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.5148</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.6397</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.7793</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.1396</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4103</v>
+        <v>-0.0814</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5417</v>
+        <v>-0.6249</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1314</v>
+        <v>0.5435</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1011</v>
@@ -2170,13 +2170,13 @@
         <v>2.7751</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5143</v>
+        <v>-0.1854</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2259</v>
+        <v>-0.3091</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2884</v>
+        <v>0.1237</v>
       </c>
       <c r="V22" t="n">
         <v>1.4033</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2549</v>
+        <v>-2.9493</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5442</v>
+        <v>-3.2386</v>
       </c>
       <c r="F23" t="n">
         <v>0.2893</v>
@@ -2248,10 +2248,10 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2827</v>
+        <v>0.0229</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2496</v>
+        <v>0.056</v>
       </c>
       <c r="U23" t="n">
         <v>-0.0331</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.034</v>
+        <v>-3.7029</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.495</v>
+        <v>-4.8006</v>
       </c>
       <c r="F24" t="n">
-        <v>0.461</v>
+        <v>1.0977</v>
       </c>
       <c r="G24" t="n">
         <v>-5.5117</v>
@@ -2326,13 +2326,13 @@
         <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2448</v>
+        <v>0.0863</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1837</v>
+        <v>-0.1219</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4285</v>
+        <v>0.2081</v>
       </c>
       <c r="V24" t="n">
         <v>0.5331</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.737</v>
+        <v>-4.3088</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3278</v>
+        <v>-5.295</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4092</v>
+        <v>0.9863</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.5623</v>
+        <v>-2.7695</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7032</v>
+        <v>-0.1235</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.859</v>
+        <v>-2.646</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8653</v>
+        <v>-1.4184</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5655</v>
+        <v>1.1374</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4308</v>
+        <v>-2.5558</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.697</v>
+        <v>-1.3511</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2688</v>
+        <v>-1.2609</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5718</v>
+        <v>-0.0902</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.9556</v>
+        <v>-1.784</v>
       </c>
       <c r="Q25" t="n">
-        <v>-6.9378</v>
+        <v>-3.9645</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1773</v>
+        <v>0.1744</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0611</v>
+        <v>-0.1787</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1162</v>
+        <v>0.3531</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6036</v>
+        <v>0.0704</v>
       </c>
       <c r="W25" t="n">
-        <v>2.4142</v>
+        <v>0.2666</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.8107</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.0826</v>
+        <v>-5.2196</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6006</v>
+        <v>-5.1428</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5181</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.7695</v>
+        <v>-1.5623</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1235</v>
+        <v>-0.7032</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.646</v>
+        <v>-0.859</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.4184</v>
+        <v>-0.8653</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1374</v>
+        <v>0.5655</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.5558</v>
+        <v>-1.4308</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.3511</v>
+        <v>-0.697</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2609</v>
+        <v>-1.2688</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0902</v>
+        <v>0.5718</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.784</v>
+        <v>-4.9556</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.9645</v>
+        <v>-6.9378</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5995</v>
+        <v>0.6947</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4844</v>
+        <v>0.2461</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1151</v>
+        <v>0.4486</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0704</v>
+        <v>0.6036</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2666</v>
+        <v>2.4142</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1962</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="27">
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.7142</v>
+        <v>-6.355999999999998</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.5568</v>
+        <v>-10.5571</v>
       </c>
       <c r="F27" t="n">
-        <v>2.8427</v>
+        <v>4.201099999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-9.374199999999998</v>
+        <v>-9.3742</v>
       </c>
       <c r="H27" t="n">
         <v>-6.0925</v>
@@ -2545,13 +2545,13 @@
         <v>-12.0639</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.9818</v>
+        <v>-8.981800000000002</v>
       </c>
       <c r="O27" t="n">
         <v>-3.0819</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.9911999999999985</v>
+        <v>-0.9911999999999983</v>
       </c>
       <c r="Q27" t="n">
         <v>-21.8044</v>
@@ -2560,13 +2560,13 @@
         <v>20.8135</v>
       </c>
       <c r="S27" t="n">
-        <v>1.2478</v>
+        <v>2.6062</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4600999999999999</v>
+        <v>0.4601000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7877000000000001</v>
+        <v>2.146</v>
       </c>
       <c r="V27" t="n">
         <v>1.4034</v>
@@ -2575,7 +2575,7 @@
         <v>8.0976</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.694599999999999</v>
+        <v>-6.6946</v>
       </c>
     </row>
   </sheetData>
